--- a/data/trans_orig/IQ09_D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D_R-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>812,54</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1400,86</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>840,06</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1186,55</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>813,75</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1066,78</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>499,04</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2207,5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>813,1</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1250,89</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>694,82</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1711,49</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>812.5443435399427</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1400.859332032475</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>840.0626043771445</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1186.55150503217</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>813.7547598730722</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1066.776459815793</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>499.0395748756764</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>2207.500559839196</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>813.1021853241982</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>1250.894220464172</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>694.822449067387</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>1711.490623556065</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>130,98; 1861,61</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>535,53; 2771,46</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>232,33; 1715,51</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>431,53; 2436,85</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,0; 1511,01</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>369,41; 1552,31</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>241,52; 720,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>701,78; 3843,43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>326,02; 1437,26</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>707,56; 2011,73</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>363,25; 1225,03</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>906,97; 2883,12</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>130.9817884290412</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>535.5269253218964</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>232.3287790017048</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>431.5311585775303</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>369.4084411004712</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>241.5233182449924</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>701.7764172466718</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>326.0166803649024</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>707.5576779448879</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>363.2499406135269</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>906.9736793656014</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1861.608746362761</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2771.456191891292</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1715.506947621465</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2436.846686018485</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1511.014042583973</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1552.306046448123</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3843.432273284684</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>1437.256343060888</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>2011.72557679846</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>1225.031433186937</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>2883.119590086419</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1706,73</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>962,24</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1518,56</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1557,64</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>796,36</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>795,96</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>873,1</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>420,52</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1390,64</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>877,22</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1167,65</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1155,25</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>786,33; 3000,93</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>500,65; 1788,56</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>821,99; 2756,26</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>918,96; 2492,73</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>368,4; 1232,38</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>400,12; 1535,74</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>311,86; 2120,42</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>161,94; 801,12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>776,06; 2358,99</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>531,03; 1348,0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>624,14; 1967,69</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>693,45; 1821,97</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1706.730141267275</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>962.2447177593341</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1518.562710829427</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1557.642558566504</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>796.3588497313091</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>795.9567303677597</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>873.0985394562067</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>420.5191833538229</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1390.641383892929</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>877.223329213125</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1167.654909068592</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1155.251347918742</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>891,11</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>175,88</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>494,15</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1945,94</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1795,74</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>744,34</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>257,33</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1159,22</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1380,68</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>420,39</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>399,35</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1631,29</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>786.3297845081364</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>500.6454291703096</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>821.9869278310623</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>918.9560032713185</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>368.4049474047778</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>400.1191012076649</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>311.8621120650486</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>161.9444549759621</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>776.0556995264031</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>531.0271971378637</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>624.1445018247491</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>693.4537757903673</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>27,74; 2481,35</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>77,73; 404,76</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>136,25; 1453,98</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>381,17; 4465,82</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>65,5; 3780,0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>260,05; 2224,93</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>32,57; 724,11</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>177,73; 2745,32</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>459,31; 2963,48</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>205,48; 1155,05</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>161,02; 972,79</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>602,76; 3333,0</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3000.930835406533</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1788.561895486519</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2756.262590964723</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2492.725412409903</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1232.381030850515</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1535.737950907075</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>2120.41707058692</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>801.1194086098049</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>2358.985130854704</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>1348.002454556982</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>1967.69054071139</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>1821.965331768587</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>749,56</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1774,66</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>549,2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1387,98</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>300,89</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>409,86</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>608,65</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1380,61</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>636,4</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1258,43</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>574,18</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1384,91</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>891.1063084262362</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>175.8798450864242</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>494.146600009473</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1945.938112733684</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1795.735660307493</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>744.3357053827473</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>257.3325155658083</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1159.2207802304</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1380.680080803713</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>420.3917958482374</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>399.3473957628012</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1631.28585615934</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>302,12; 1404,05</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>802,76; 2974,01</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>139,52; 1705,79</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>695,96; 2222,37</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20,43; 720,0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>153,13; 1009,04</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>239,23; 1148,19</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>554,89; 2119,4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>278,91; 1227,36</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>572,83; 2209,13</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>279,21; 1296,45</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>780,85; 1947,59</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>27.73649333009907</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>77.73098084259603</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>136.2485304731531</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>380.0371837649361</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>65.49872110047717</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>260.0490776899909</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>32.56732925452789</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>164.198687567854</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>459.3091706827886</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>205.4757074020212</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>161.0180766047696</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>602.7554365930279</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2481.351185811577</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>404.7567481092663</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1453.983803547882</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4464.146215339269</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>3780</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2224.925311281853</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>724.113745887121</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2731.626372932017</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>2963.480863724639</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>1155.047528778913</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>972.7856819669536</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>3332.996233200175</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>749.5587705980578</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1774.657574859707</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>549.2033819844819</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1387.982942112317</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>300.8910076308758</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>409.8607674652842</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>608.6521695868851</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>1380.609297901326</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>636.4048805766347</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1258.428363079887</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>574.177793945233</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>1384.905644062036</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>302.1247399910944</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>802.7564554948747</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>139.5150427122977</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>695.9621679096269</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>20.43309115266247</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>153.1254064117263</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>239.2280561029303</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>554.8866050125945</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>278.9109248000657</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>572.8250531084797</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>279.2145402432918</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>780.8496463822357</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1404.047748234632</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2974.014696813911</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1705.792883271139</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2222.370377298781</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1009.037786549406</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1148.188839019298</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>2119.399213206024</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1227.360428018643</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>2209.130818873067</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>1296.447738804433</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>1947.594930657927</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1140,05</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1015,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>878,68</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1548,94</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>948,85</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>766,17</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>644,63</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1224,52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1068,67</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>904,17</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>770,93</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1416,45</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>687,48; 1792,19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>667,1; 1558,09</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>556,59; 1408,77</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1073,15; 2249,67</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>507,61; 1677,19</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>513,86; 1174,61</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>417,53; 1255,2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>710,43; 1905,84</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>729,78; 1512,38</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>636,68; 1200,57</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>530,89; 1109,19</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1054,93; 1957,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1140.052331090635</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1015.572102988115</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>878.6814384510232</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1548.936425072869</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>948.8454535284831</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>766.167992932946</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>644.6346331759288</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>1224.524897460577</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1068.672074903559</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>904.1696260003995</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>770.9292778379756</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1416.445268064866</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>687.4783662625334</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>667.0953950035024</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>556.5907179458264</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1073.152880172508</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>507.6127131815576</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>513.8647119367296</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>417.5331589457379</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>710.4256136466851</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>729.7814094032586</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>636.683035396911</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>530.894379708471</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>1054.93426473185</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1792.193224790381</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1558.09463697483</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1408.771766777626</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2249.673011307639</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1677.189912112222</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1174.605140710644</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1255.196537176316</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>1905.838597281182</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1512.383458756617</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>1200.571417420908</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>1109.185444747269</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1957.542433894739</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
